--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.4012804215974</v>
+        <v>9.002708068509577</v>
       </c>
       <c r="D2" t="n">
-        <v>55.38814523072896</v>
+        <v>9.000573599993457</v>
       </c>
       <c r="E2" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F2" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.95741651032769</v>
+        <v>5.51808018292825</v>
       </c>
       <c r="D3" t="n">
-        <v>33.9742542805656</v>
+        <v>5.520816320591909</v>
       </c>
       <c r="E3" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F3" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.16850435619176</v>
+        <v>1.652381957881161</v>
       </c>
       <c r="D4" t="n">
-        <v>10.28926632659381</v>
+        <v>1.672005778071495</v>
       </c>
       <c r="E4" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F4" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.96502177624663</v>
+        <v>4.544316038640077</v>
       </c>
       <c r="D5" t="n">
-        <v>28.58924660829922</v>
+        <v>4.645752573848624</v>
       </c>
       <c r="E5" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F5" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.56218874182372</v>
+        <v>6.753855670546354</v>
       </c>
       <c r="D6" t="n">
-        <v>41.54362338177756</v>
+        <v>6.750838799538854</v>
       </c>
       <c r="E6" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F6" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.84841122594322</v>
+        <v>4.525366824215773</v>
       </c>
       <c r="D7" t="n">
-        <v>28.23446194183794</v>
+        <v>4.588100065548666</v>
       </c>
       <c r="E7" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F7" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.87741989696412</v>
+        <v>4.367580733256671</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95824605564313</v>
+        <v>4.380714984042008</v>
       </c>
       <c r="E8" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F8" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.91162657638571</v>
+        <v>3.560639318662679</v>
       </c>
       <c r="D9" t="n">
-        <v>21.28148925111839</v>
+        <v>3.458242003306739</v>
       </c>
       <c r="E9" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F9" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.13323149075137</v>
+        <v>4.734150117247097</v>
       </c>
       <c r="D10" t="n">
-        <v>28.50286419890174</v>
+        <v>4.631715432321534</v>
       </c>
       <c r="E10" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F10" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.06238296405612</v>
+        <v>4.56013723165912</v>
       </c>
       <c r="D11" t="n">
-        <v>27.97702595697923</v>
+        <v>4.546266718009125</v>
       </c>
       <c r="E11" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F11" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.27723795339584</v>
+        <v>4.757551167426825</v>
       </c>
       <c r="D12" t="n">
-        <v>29.3300063803709</v>
+        <v>4.766126036810272</v>
       </c>
       <c r="E12" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F12" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>49.59053483186799</v>
+        <v>8.058461910178549</v>
       </c>
       <c r="D13" t="n">
-        <v>48.96067877392544</v>
+        <v>7.956110300762884</v>
       </c>
       <c r="E13" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F13" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>44.29422506048003</v>
+        <v>7.197811572328005</v>
       </c>
       <c r="D14" t="n">
-        <v>44.29199488047941</v>
+        <v>7.197449168077905</v>
       </c>
       <c r="E14" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F14" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>58.85973771722185</v>
+        <v>9.564707379048551</v>
       </c>
       <c r="D15" t="n">
-        <v>58.94844470148376</v>
+        <v>9.579122263991112</v>
       </c>
       <c r="E15" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F15" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>61.25531240940747</v>
+        <v>9.953988266528713</v>
       </c>
       <c r="D16" t="n">
-        <v>61.28571479981783</v>
+        <v>9.958928654970398</v>
       </c>
       <c r="E16" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F16" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>89.53317685930668</v>
+        <v>14.54914123963734</v>
       </c>
       <c r="D17" t="n">
-        <v>89.60685407824869</v>
+        <v>14.56111378771541</v>
       </c>
       <c r="E17" t="n">
-        <v>18.88089389583986</v>
+        <v>3.068145258073977</v>
       </c>
       <c r="F17" t="n">
-        <v>18.88802618647575</v>
+        <v>3.069304255302309</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
